--- a/research/traditional_assets/database/data/romania/romania_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0708</v>
+        <v>0.185</v>
       </c>
       <c r="E2">
-        <v>0.122</v>
+        <v>0.322</v>
       </c>
       <c r="G2">
-        <v>0.07548076923076923</v>
+        <v>0.08669354838709677</v>
       </c>
       <c r="H2">
-        <v>0.07548076923076923</v>
+        <v>0.07862903225806452</v>
       </c>
       <c r="I2">
-        <v>0.08605769230769231</v>
+        <v>0.08991935483870968</v>
       </c>
       <c r="J2">
-        <v>0.07445440795159897</v>
+        <v>0.07641129032258065</v>
       </c>
       <c r="K2">
-        <v>1.54</v>
+        <v>1.89</v>
       </c>
       <c r="L2">
-        <v>0.07403846153846154</v>
+        <v>0.07620967741935483</v>
       </c>
       <c r="M2">
-        <v>1.0075</v>
+        <v>1.485</v>
       </c>
       <c r="N2">
-        <v>0.05140306122448979</v>
+        <v>0.07774869109947642</v>
       </c>
       <c r="O2">
-        <v>0.6542207792207793</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="P2">
-        <v>1.0075</v>
+        <v>1.485</v>
       </c>
       <c r="Q2">
-        <v>0.05140306122448979</v>
+        <v>0.07774869109947642</v>
       </c>
       <c r="R2">
-        <v>0.6542207792207793</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,64 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2.91</v>
+        <v>2.21</v>
       </c>
       <c r="V2">
-        <v>0.148469387755102</v>
+        <v>0.1157068062827225</v>
       </c>
       <c r="W2">
-        <v>1.019867549668874</v>
+        <v>0.945</v>
       </c>
       <c r="X2">
-        <v>0.06065844542561809</v>
+        <v>0.09934288059738128</v>
       </c>
       <c r="Y2">
-        <v>0.9592091042432562</v>
-      </c>
-      <c r="Z2">
-        <v>113.6612021857925</v>
-      </c>
-      <c r="AA2">
-        <v>8.462577515810162</v>
+        <v>0.8456571194026187</v>
       </c>
       <c r="AB2">
-        <v>0.05986040311617113</v>
-      </c>
-      <c r="AC2">
-        <v>8.402717112693992</v>
+        <v>0.09852034631392552</v>
       </c>
       <c r="AD2">
-        <v>0.638</v>
+        <v>0.434</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.638</v>
+        <v>0.434</v>
       </c>
       <c r="AG2">
-        <v>-2.272</v>
+        <v>-1.776</v>
       </c>
       <c r="AH2">
-        <v>0.03152485423460816</v>
+        <v>0.02221767175181734</v>
       </c>
       <c r="AI2">
-        <v>0.241849886277483</v>
+        <v>0.1712707182320442</v>
       </c>
       <c r="AJ2">
-        <v>-0.1311172668513389</v>
+        <v>-0.1025167397829601</v>
       </c>
       <c r="AK2">
-        <v>8.352941176470582</v>
+        <v>-5.48148148148148</v>
       </c>
       <c r="AL2">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="AM2">
-        <v>0.015</v>
+        <v>0.001999999999999998</v>
       </c>
       <c r="AN2">
-        <v>0.3448648648648648</v>
+        <v>0.1895196506550218</v>
       </c>
       <c r="AO2">
-        <v>77.82608695652175</v>
+        <v>101.3636363636364</v>
       </c>
       <c r="AP2">
-        <v>-1.228108108108108</v>
+        <v>-0.7755458515283843</v>
       </c>
       <c r="AQ2">
-        <v>119.3333333333333</v>
+        <v>1115.000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +713,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0708</v>
+        <v>0.185</v>
       </c>
       <c r="E3">
-        <v>0.122</v>
+        <v>0.322</v>
       </c>
       <c r="G3">
-        <v>0.07548076923076923</v>
+        <v>0.08669354838709677</v>
       </c>
       <c r="H3">
-        <v>0.07548076923076923</v>
+        <v>0.07862903225806452</v>
       </c>
       <c r="I3">
-        <v>0.08605769230769231</v>
+        <v>0.08991935483870968</v>
       </c>
       <c r="J3">
-        <v>0.07445440795159897</v>
+        <v>0.07641129032258065</v>
       </c>
       <c r="K3">
-        <v>1.54</v>
+        <v>1.89</v>
       </c>
       <c r="L3">
-        <v>0.07403846153846154</v>
+        <v>0.07620967741935483</v>
       </c>
       <c r="M3">
-        <v>1.0075</v>
+        <v>1.485</v>
       </c>
       <c r="N3">
-        <v>0.05140306122448979</v>
+        <v>0.07774869109947642</v>
       </c>
       <c r="O3">
-        <v>0.6542207792207793</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="P3">
-        <v>1.0075</v>
+        <v>1.485</v>
       </c>
       <c r="Q3">
-        <v>0.05140306122448979</v>
+        <v>0.07774869109947642</v>
       </c>
       <c r="R3">
-        <v>0.6542207792207793</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +761,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.91</v>
+        <v>2.21</v>
       </c>
       <c r="V3">
-        <v>0.148469387755102</v>
+        <v>0.1157068062827225</v>
       </c>
       <c r="W3">
-        <v>1.019867549668874</v>
+        <v>0.945</v>
       </c>
       <c r="X3">
-        <v>0.06065844542561809</v>
+        <v>0.09934288059738128</v>
       </c>
       <c r="Y3">
-        <v>0.9592091042432562</v>
-      </c>
-      <c r="Z3">
-        <v>113.6612021857925</v>
-      </c>
-      <c r="AA3">
-        <v>8.462577515810162</v>
+        <v>0.8456571194026187</v>
       </c>
       <c r="AB3">
-        <v>0.05986040311617113</v>
-      </c>
-      <c r="AC3">
-        <v>8.402717112693992</v>
+        <v>0.09852034631392552</v>
       </c>
       <c r="AD3">
-        <v>0.638</v>
+        <v>0.434</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.638</v>
+        <v>0.434</v>
       </c>
       <c r="AG3">
-        <v>-2.272</v>
+        <v>-1.776</v>
       </c>
       <c r="AH3">
-        <v>0.03152485423460816</v>
+        <v>0.02221767175181734</v>
       </c>
       <c r="AI3">
-        <v>0.241849886277483</v>
+        <v>0.1712707182320442</v>
       </c>
       <c r="AJ3">
-        <v>-0.1311172668513389</v>
+        <v>-0.1025167397829601</v>
       </c>
       <c r="AK3">
-        <v>8.352941176470582</v>
+        <v>-5.48148148148148</v>
       </c>
       <c r="AL3">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="AM3">
-        <v>0.015</v>
+        <v>0.001999999999999998</v>
       </c>
       <c r="AN3">
-        <v>0.3448648648648648</v>
+        <v>0.1895196506550218</v>
       </c>
       <c r="AO3">
-        <v>77.82608695652175</v>
+        <v>101.3636363636364</v>
       </c>
       <c r="AP3">
-        <v>-1.228108108108108</v>
+        <v>-0.7755458515283843</v>
       </c>
       <c r="AQ3">
-        <v>119.3333333333333</v>
+        <v>1115.000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/romania/romania_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_insurance_general.xlsx
@@ -588,112 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.185</v>
+        <v>0.148</v>
       </c>
       <c r="E2">
-        <v>0.322</v>
+        <v>0.204</v>
       </c>
       <c r="G2">
-        <v>0.08669354838709677</v>
+        <v>0.1176706827309237</v>
       </c>
       <c r="H2">
-        <v>0.07862903225806452</v>
+        <v>0.1176706827309237</v>
       </c>
       <c r="I2">
-        <v>0.08991935483870968</v>
+        <v>0.09357429718875503</v>
       </c>
       <c r="J2">
-        <v>0.07641129032258065</v>
+        <v>0.08138245929777201</v>
       </c>
       <c r="K2">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="L2">
-        <v>0.07620967741935483</v>
+        <v>0.08433734939759037</v>
       </c>
       <c r="M2">
-        <v>1.485</v>
+        <v>2.152</v>
       </c>
       <c r="N2">
-        <v>0.07774869109947642</v>
+        <v>0.088559670781893</v>
       </c>
       <c r="O2">
-        <v>0.7857142857142857</v>
+        <v>1.024761904761905</v>
       </c>
       <c r="P2">
-        <v>1.485</v>
+        <v>2.125</v>
       </c>
       <c r="Q2">
-        <v>0.07774869109947642</v>
+        <v>0.08744855967078188</v>
       </c>
       <c r="R2">
-        <v>0.7857142857142857</v>
+        <v>1.011904761904762</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.02700000000000014</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.01254646840148705</v>
       </c>
       <c r="U2">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="V2">
-        <v>0.1157068062827225</v>
+        <v>0.08024691358024691</v>
       </c>
       <c r="W2">
-        <v>0.945</v>
+        <v>1</v>
       </c>
       <c r="X2">
-        <v>0.09934288059738128</v>
+        <v>0.08793521266425729</v>
       </c>
       <c r="Y2">
-        <v>0.8456571194026187</v>
+        <v>0.9120647873357427</v>
+      </c>
+      <c r="Z2">
+        <v>76.85185185185178</v>
+      </c>
+      <c r="AA2">
+        <v>6.254392705291732</v>
       </c>
       <c r="AB2">
-        <v>0.09852034631392552</v>
+        <v>0.0875779626428855</v>
+      </c>
+      <c r="AC2">
+        <v>6.166814742648846</v>
       </c>
       <c r="AD2">
-        <v>0.434</v>
+        <v>0.293</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.434</v>
+        <v>0.293</v>
       </c>
       <c r="AG2">
-        <v>-1.776</v>
+        <v>-1.657</v>
       </c>
       <c r="AH2">
-        <v>0.02221767175181734</v>
+        <v>0.01191395925669906</v>
       </c>
       <c r="AI2">
-        <v>0.1712707182320442</v>
+        <v>0.1161315893777249</v>
       </c>
       <c r="AJ2">
-        <v>-0.1025167397829601</v>
+        <v>-0.07317934902618911</v>
       </c>
       <c r="AK2">
-        <v>-5.48148148148148</v>
+        <v>-2.891797556719023</v>
       </c>
       <c r="AL2">
-        <v>0.022</v>
+        <v>0.037</v>
       </c>
       <c r="AM2">
-        <v>0.001999999999999998</v>
+        <v>-0.04700000000000001</v>
       </c>
       <c r="AN2">
-        <v>0.1895196506550218</v>
+        <v>0.1215767634854772</v>
       </c>
       <c r="AO2">
-        <v>101.3636363636364</v>
+        <v>62.97297297297298</v>
       </c>
       <c r="AP2">
-        <v>-0.7755458515283843</v>
+        <v>-0.687551867219917</v>
       </c>
       <c r="AQ2">
-        <v>1115.000000000001</v>
+        <v>-49.57446808510637</v>
       </c>
     </row>
     <row r="3">
@@ -713,112 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.185</v>
+        <v>0.148</v>
       </c>
       <c r="E3">
-        <v>0.322</v>
+        <v>0.204</v>
       </c>
       <c r="G3">
-        <v>0.08669354838709677</v>
+        <v>0.1176706827309237</v>
       </c>
       <c r="H3">
-        <v>0.07862903225806452</v>
+        <v>0.1176706827309237</v>
       </c>
       <c r="I3">
-        <v>0.08991935483870968</v>
+        <v>0.09357429718875503</v>
       </c>
       <c r="J3">
-        <v>0.07641129032258065</v>
+        <v>0.08138245929777201</v>
       </c>
       <c r="K3">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="L3">
-        <v>0.07620967741935483</v>
+        <v>0.08433734939759037</v>
       </c>
       <c r="M3">
-        <v>1.485</v>
+        <v>2.152</v>
       </c>
       <c r="N3">
-        <v>0.07774869109947642</v>
+        <v>0.088559670781893</v>
       </c>
       <c r="O3">
-        <v>0.7857142857142857</v>
+        <v>1.024761904761905</v>
       </c>
       <c r="P3">
-        <v>1.485</v>
+        <v>2.125</v>
       </c>
       <c r="Q3">
-        <v>0.07774869109947642</v>
+        <v>0.08744855967078188</v>
       </c>
       <c r="R3">
-        <v>0.7857142857142857</v>
+        <v>1.011904761904762</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.02700000000000014</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.01254646840148705</v>
       </c>
       <c r="U3">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="V3">
-        <v>0.1157068062827225</v>
+        <v>0.08024691358024691</v>
       </c>
       <c r="W3">
-        <v>0.945</v>
+        <v>1</v>
       </c>
       <c r="X3">
-        <v>0.09934288059738128</v>
+        <v>0.08793521266425729</v>
       </c>
       <c r="Y3">
-        <v>0.8456571194026187</v>
+        <v>0.9120647873357427</v>
+      </c>
+      <c r="Z3">
+        <v>76.85185185185178</v>
+      </c>
+      <c r="AA3">
+        <v>6.254392705291732</v>
       </c>
       <c r="AB3">
-        <v>0.09852034631392552</v>
+        <v>0.0875779626428855</v>
+      </c>
+      <c r="AC3">
+        <v>6.166814742648846</v>
       </c>
       <c r="AD3">
-        <v>0.434</v>
+        <v>0.293</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.434</v>
+        <v>0.293</v>
       </c>
       <c r="AG3">
-        <v>-1.776</v>
+        <v>-1.657</v>
       </c>
       <c r="AH3">
-        <v>0.02221767175181734</v>
+        <v>0.01191395925669906</v>
       </c>
       <c r="AI3">
-        <v>0.1712707182320442</v>
+        <v>0.1161315893777249</v>
       </c>
       <c r="AJ3">
-        <v>-0.1025167397829601</v>
+        <v>-0.07317934902618911</v>
       </c>
       <c r="AK3">
-        <v>-5.48148148148148</v>
+        <v>-2.891797556719023</v>
       </c>
       <c r="AL3">
-        <v>0.022</v>
+        <v>0.037</v>
       </c>
       <c r="AM3">
-        <v>0.001999999999999998</v>
+        <v>-0.04700000000000001</v>
       </c>
       <c r="AN3">
-        <v>0.1895196506550218</v>
+        <v>0.1215767634854772</v>
       </c>
       <c r="AO3">
-        <v>101.3636363636364</v>
+        <v>62.97297297297298</v>
       </c>
       <c r="AP3">
-        <v>-0.7755458515283843</v>
+        <v>-0.687551867219917</v>
       </c>
       <c r="AQ3">
-        <v>1115.000000000001</v>
+        <v>-49.57446808510637</v>
       </c>
     </row>
   </sheetData>
